--- a/output/DE/output_DE_MIP_testCP3.xlsx
+++ b/output/DE/output_DE_MIP_testCP3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="5">
@@ -577,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="6">
@@ -605,7 +605,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>139.88</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="7">
@@ -633,7 +633,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="8">
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.44</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="9">
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>9.57</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="10">
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1801.15</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="11">
@@ -738,390 +738,12 @@
       <c r="E11" t="n">
         <v>24</v>
       </c>
-      <c r="F11" t="n">
-        <v>17</v>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1802.92</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>J-nos4.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>100</v>
-      </c>
-      <c r="C12" t="n">
-        <v>56</v>
-      </c>
-      <c r="D12" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" t="n">
-        <v>36</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>560.71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>K-dwt__234.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>117</v>
-      </c>
-      <c r="C13" t="n">
-        <v>80</v>
-      </c>
-      <c r="D13" t="n">
-        <v>31</v>
-      </c>
-      <c r="E13" t="n">
-        <v>51</v>
-      </c>
-      <c r="F13" t="n">
-        <v>39</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>443.42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>L-bcspwr03.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>118</v>
-      </c>
-      <c r="C14" t="n">
-        <v>62</v>
-      </c>
-      <c r="D14" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" t="n">
-        <v>39</v>
-      </c>
-      <c r="F14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1816.17</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>M-bcsstk06.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>420</v>
-      </c>
-      <c r="C15" t="n">
-        <v>323</v>
-      </c>
-      <c r="D15" t="n">
-        <v>21</v>
-      </c>
-      <c r="E15" t="n">
-        <v>35</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1806.99</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>O-impcol_d.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>425</v>
-      </c>
-      <c r="C16" t="n">
-        <v>221</v>
-      </c>
-      <c r="D16" t="n">
-        <v>47</v>
-      </c>
-      <c r="E16" t="n">
-        <v>102</v>
-      </c>
-      <c r="F16" t="n">
-        <v>54</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1809.15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>P-can__445.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>445</v>
-      </c>
-      <c r="C17" t="n">
-        <v>333</v>
-      </c>
-      <c r="D17" t="n">
-        <v>58</v>
-      </c>
-      <c r="E17" t="n">
-        <v>79</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1821.74</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Q-494_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>494</v>
-      </c>
-      <c r="C18" t="n">
-        <v>326</v>
-      </c>
-      <c r="D18" t="n">
-        <v>144</v>
-      </c>
-      <c r="E18" t="n">
-        <v>220</v>
-      </c>
-      <c r="F18" t="n">
-        <v>152</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1806.39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-dwt__503.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>503</v>
-      </c>
-      <c r="C19" t="n">
-        <v>347</v>
-      </c>
-      <c r="D19" t="n">
-        <v>31</v>
-      </c>
-      <c r="E19" t="n">
-        <v>64</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1820.33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S-sherman4.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>546</v>
-      </c>
-      <c r="C20" t="n">
-        <v>322</v>
-      </c>
-      <c r="D20" t="n">
-        <v>151</v>
-      </c>
-      <c r="E20" t="n">
-        <v>256</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1823.23</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T-dwt__592.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>592</v>
-      </c>
-      <c r="C21" t="n">
-        <v>378</v>
-      </c>
-      <c r="D21" t="n">
-        <v>65</v>
-      </c>
-      <c r="E21" t="n">
-        <v>104</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1814.66</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U-662_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>662</v>
-      </c>
-      <c r="C22" t="n">
-        <v>516</v>
-      </c>
-      <c r="D22" t="n">
-        <v>170</v>
-      </c>
-      <c r="E22" t="n">
-        <v>220</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1822.99</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>V-nos6.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>675</v>
-      </c>
-      <c r="C23" t="n">
-        <v>405</v>
-      </c>
-      <c r="D23" t="n">
-        <v>195</v>
-      </c>
-      <c r="E23" t="n">
-        <v>326</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1817.22</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>W-685_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>685</v>
-      </c>
-      <c r="C24" t="n">
-        <v>397</v>
-      </c>
-      <c r="D24" t="n">
-        <v>78</v>
-      </c>
-      <c r="E24" t="n">
-        <v>136</v>
-      </c>
-      <c r="F24" t="n">
-        <v>78</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1820.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>X-can__715.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>715</v>
-      </c>
-      <c r="C25" t="n">
-        <v>500</v>
-      </c>
-      <c r="D25" t="n">
-        <v>78</v>
-      </c>
-      <c r="E25" t="n">
-        <v>113</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1806.87</v>
+        <v>4.01</v>
       </c>
     </row>
   </sheetData>
